--- a/src/files/archivo_actualizado_ciael.xlsx
+++ b/src/files/archivo_actualizado_ciael.xlsx
@@ -2757,7 +2757,7 @@
         <v>135</v>
       </c>
       <c r="G11" s="15">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H11" t="s" s="14">
         <v>136</v>
